--- a/02_Input/capital.xlsx
+++ b/02_Input/capital.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eceta\OneDrive\Desktop\BSE\02_TERM_2\MACRO_I\BSE_Macro_Accounters\02_Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40EB64A8-26CE-4DCB-8181-BAF752DB9396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C18CA4-4E0B-49A6-B755-F370744B80E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1115,14 +1115,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3018E266-C25C-46DE-A715-AAC840672269}">
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.5546875" customWidth="1"/>
     <col min="3" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1136,7 +1138,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1150,7 +1152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1164,7 +1166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1178,7 +1180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1192,7 +1194,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1209,8 +1211,16 @@
         <f t="shared" ref="E6:E29" si="0">C6/D6*100</f>
         <v>90.768480633337063</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <f>C6/B6*100</f>
+        <v>423889093.67363918</v>
+      </c>
+      <c r="G6">
+        <f>F6-D6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1227,8 +1237,16 @@
         <f t="shared" si="0"/>
         <v>91.105098014390961</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <f t="shared" ref="F7:F32" si="1">C7/B7*100</f>
+        <v>437074253.84412575</v>
+      </c>
+      <c r="G7">
+        <f t="shared" ref="G7:G32" si="2">F7-D7</f>
+        <v>7.7486038208007813E-7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1245,8 +1263,16 @@
         <f t="shared" si="0"/>
         <v>92.598701965328104</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>446074984.92714697</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="2"/>
+        <v>-1.0132789611816406E-6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1263,8 +1289,16 @@
         <f t="shared" si="0"/>
         <v>90.921905826137291</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>450034403.60511744</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="2"/>
+        <v>-5.3644180297851563E-7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1281,8 +1315,16 @@
         <f t="shared" si="0"/>
         <v>89.747147073382621</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>453704441.2072435</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="2"/>
+        <v>-4.76837158203125E-7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1299,8 +1341,16 @@
         <f t="shared" si="0"/>
         <v>89.646669278276477</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>457311524.39185381</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1317,8 +1367,16 @@
         <f t="shared" si="0"/>
         <v>88.658864036473517</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>459763493.92085457</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1335,8 +1393,16 @@
         <f t="shared" si="0"/>
         <v>87.519895332353784</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>461306612.40031302</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="2"/>
+        <v>1.0132789611816406E-6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1353,8 +1419,16 @@
         <f t="shared" si="0"/>
         <v>87.287499376088874</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>462514544.62900531</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1371,8 +1445,16 @@
         <f t="shared" si="0"/>
         <v>87.433980808965345</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>464360794.6562072</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1389,8 +1471,16 @@
         <f t="shared" si="0"/>
         <v>87.670907648872586</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>465950617.70086342</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1407,8 +1497,16 @@
         <f t="shared" si="0"/>
         <v>88.860364538881925</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17">
+        <f t="shared" si="1"/>
+        <v>467475515.08203661</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -1425,8 +1523,16 @@
         <f t="shared" si="0"/>
         <v>90.56212901865203</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <f t="shared" si="1"/>
+        <v>466252446.33462864</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1443,8 +1549,16 @@
         <f t="shared" si="0"/>
         <v>92.879366803518423</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19">
+        <f t="shared" si="1"/>
+        <v>463511190.23891419</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="2"/>
+        <v>-8.3446502685546875E-7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -1461,8 +1575,16 @@
         <f t="shared" si="0"/>
         <v>90.88201519189289</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20">
+        <f t="shared" si="1"/>
+        <v>456859429.32465702</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1479,8 +1601,16 @@
         <f t="shared" si="0"/>
         <v>90.016991171235532</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21">
+        <f t="shared" si="1"/>
+        <v>450295987.38842916</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1497,8 +1627,16 @@
         <f t="shared" si="0"/>
         <v>90.055440587743291</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F22">
+        <f t="shared" si="1"/>
+        <v>445355688.86328989</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1515,8 +1653,16 @@
         <f t="shared" si="0"/>
         <v>89.411222841625516</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23">
+        <f t="shared" si="1"/>
+        <v>441137532.75783157</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="2"/>
+        <v>5.9604644775390625E-7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -1533,8 +1679,16 @@
         <f t="shared" si="0"/>
         <v>91.013507078068457</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24">
+        <f t="shared" si="1"/>
+        <v>438979169.3187573</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1551,8 +1705,16 @@
         <f t="shared" si="0"/>
         <v>94.07219462224316</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F25">
+        <f t="shared" si="1"/>
+        <v>436411901.30772179</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -1569,8 +1731,16 @@
         <f t="shared" si="0"/>
         <v>94.978431105842915</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F26">
+        <f t="shared" si="1"/>
+        <v>433932138.06886768</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -1587,8 +1757,16 @@
         <f t="shared" si="0"/>
         <v>94.507931723350254</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F27">
+        <f t="shared" si="1"/>
+        <v>432432183.17763841</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="2"/>
+        <v>-5.9604644775390625E-7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1605,8 +1783,16 @@
         <f t="shared" si="0"/>
         <v>96.134018598428725</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F28">
+        <f t="shared" si="1"/>
+        <v>430975116.19536567</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -1623,8 +1809,16 @@
         <f t="shared" si="0"/>
         <v>97.736859443599613</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F29">
+        <f t="shared" si="1"/>
+        <v>428119551.38494104</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -1641,8 +1835,16 @@
         <f>C30/D30*100</f>
         <v>98.968026039498767</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F30">
+        <f t="shared" si="1"/>
+        <v>426211053.02809346</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="2"/>
+        <v>-5.3644180297851563E-7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -1659,8 +1861,16 @@
         <f>C31/D31</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F31">
+        <f t="shared" si="1"/>
+        <v>422672707.42670399</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -1674,6 +1884,14 @@
         <v>0</v>
       </c>
       <c r="E32" s="1"/>
+      <c r="F32" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G32" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
